--- a/data/CAPS_RFP_Dashboard_Dataset.xlsx
+++ b/data/CAPS_RFP_Dashboard_Dataset.xlsx
@@ -2083,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1115"/>
+  <dimension ref="A1:AA1186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -51096,7 +51096,7 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -51104,10 +51104,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J680" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
+      <c r="J680" s="96" t="n">
+        <v>46273</v>
       </c>
       <c r="K680" t="inlineStr">
         <is>
@@ -56151,7 +56149,7 @@
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -56160,7 +56158,7 @@
         </is>
       </c>
       <c r="J753" s="96" t="n">
-        <v>46168</v>
+        <v>46273</v>
       </c>
       <c r="K753" s="96" t="n">
         <v>46168</v>
@@ -56939,7 +56937,7 @@
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>RFx Cancelled</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
@@ -58540,7 +58538,7 @@
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -58549,7 +58547,7 @@
         </is>
       </c>
       <c r="J789" s="96" t="n">
-        <v>46177</v>
+        <v>46266</v>
       </c>
       <c r="K789" s="96" t="n">
         <v>46177</v>
@@ -59962,6 +59960,9 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
+      <c r="Q810" s="96" t="n">
+        <v>46240</v>
+      </c>
       <c r="Y810" s="96" t="n">
         <v>46148</v>
       </c>
@@ -60902,7 +60903,7 @@
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
@@ -60911,7 +60912,7 @@
         </is>
       </c>
       <c r="J825" s="96" t="n">
-        <v>46189</v>
+        <v>46260</v>
       </c>
       <c r="K825" s="96" t="n">
         <v>46189</v>
@@ -61090,7 +61091,7 @@
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
@@ -61099,7 +61100,7 @@
         </is>
       </c>
       <c r="J828" s="96" t="n">
-        <v>46190</v>
+        <v>46266</v>
       </c>
       <c r="K828" s="96" t="n">
         <v>46189</v>
@@ -61348,6 +61349,9 @@
           <t>Savya Atrey</t>
         </is>
       </c>
+      <c r="Q832" s="96" t="n">
+        <v>46240</v>
+      </c>
       <c r="Y832" s="96" t="n">
         <v>46164</v>
       </c>
@@ -65331,7 +65335,7 @@
       </c>
       <c r="G897" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H897" t="inlineStr">
@@ -65340,7 +65344,7 @@
         </is>
       </c>
       <c r="J897" s="96" t="n">
-        <v>46199</v>
+        <v>46273</v>
       </c>
       <c r="K897" s="96" t="n">
         <v>46199</v>
@@ -65508,7 +65512,7 @@
       </c>
       <c r="G900" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H900" t="inlineStr">
@@ -65517,10 +65521,13 @@
         </is>
       </c>
       <c r="J900" s="96" t="n">
-        <v>46195</v>
+        <v>46266</v>
       </c>
       <c r="K900" s="96" t="n">
         <v>46195</v>
+      </c>
+      <c r="L900" t="n">
+        <v>2559000</v>
       </c>
       <c r="M900" t="inlineStr">
         <is>
@@ -69128,7 +69135,7 @@
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H962" t="inlineStr">
@@ -69137,7 +69144,7 @@
         </is>
       </c>
       <c r="J962" s="96" t="n">
-        <v>46204</v>
+        <v>46273</v>
       </c>
       <c r="K962" s="96" t="n">
         <v>46203</v>
@@ -69264,7 +69271,7 @@
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H964" t="inlineStr">
@@ -69273,7 +69280,7 @@
         </is>
       </c>
       <c r="J964" s="96" t="n">
-        <v>46204</v>
+        <v>46273</v>
       </c>
       <c r="K964" s="96" t="n">
         <v>46203</v>
@@ -69333,7 +69340,7 @@
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>Intent to Award</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
@@ -69342,7 +69349,7 @@
         </is>
       </c>
       <c r="J965" s="96" t="n">
-        <v>46202</v>
+        <v>46268</v>
       </c>
       <c r="K965" s="96" t="n">
         <v>46202</v>
@@ -70182,6 +70189,9 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
+      <c r="Q978" s="96" t="n">
+        <v>46241</v>
+      </c>
       <c r="Y978" s="96" t="n">
         <v>46176</v>
       </c>
@@ -72825,7 +72835,7 @@
       </c>
       <c r="G1022" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr">
@@ -72834,7 +72844,7 @@
         </is>
       </c>
       <c r="J1022" s="96" t="n">
-        <v>46230</v>
+        <v>46260</v>
       </c>
       <c r="K1022" s="96" t="n">
         <v>46230</v>
@@ -72933,7 +72943,7 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>North Dakota Department of Health and Human Services Rural Health Transformation Program (RHTP)</t>
+          <t>North Dakota Department of Health and Human Services RHTP</t>
         </is>
       </c>
       <c r="F1024" t="inlineStr">
@@ -73200,7 +73210,7 @@
       </c>
       <c r="G1028" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H1028" t="inlineStr">
@@ -73221,6 +73231,9 @@
       </c>
       <c r="Q1028" s="96" t="n">
         <v>46247</v>
+      </c>
+      <c r="S1028" s="96" t="n">
+        <v>46258</v>
       </c>
       <c r="Y1028" s="96" t="n">
         <v>46213</v>
@@ -73985,7 +73998,7 @@
       </c>
       <c r="G1041" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H1041" t="inlineStr">
@@ -73994,7 +74007,7 @@
         </is>
       </c>
       <c r="J1041" s="96" t="n">
-        <v>46234</v>
+        <v>46260</v>
       </c>
       <c r="K1041" s="96" t="n">
         <v>46233</v>
@@ -74224,7 +74237,7 @@
       </c>
       <c r="G1045" t="inlineStr">
         <is>
-          <t>Interview</t>
+          <t>Closed Won</t>
         </is>
       </c>
       <c r="H1045" t="inlineStr">
@@ -74233,7 +74246,7 @@
         </is>
       </c>
       <c r="J1045" s="96" t="n">
-        <v>46237</v>
+        <v>46265</v>
       </c>
       <c r="K1045" s="96" t="n">
         <v>46237</v>
@@ -74250,6 +74263,9 @@
       </c>
       <c r="Q1045" s="96" t="n">
         <v>46251</v>
+      </c>
+      <c r="U1045" s="96" t="n">
+        <v>46254</v>
       </c>
       <c r="Y1045" s="96" t="n">
         <v>46226</v>
@@ -74367,7 +74383,7 @@
         <v>46240</v>
       </c>
       <c r="K1047" s="96" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="M1047" t="inlineStr">
         <is>
@@ -75597,7 +75613,7 @@
       </c>
       <c r="G1067" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Interview</t>
         </is>
       </c>
       <c r="H1067" t="inlineStr">
@@ -75628,6 +75644,9 @@
         <is>
           <t>Yash More</t>
         </is>
+      </c>
+      <c r="Q1067" s="96" t="n">
+        <v>46267</v>
       </c>
       <c r="Y1067" s="96" t="n">
         <v>46199</v>
@@ -78431,7 +78450,7 @@
       </c>
       <c r="G1113" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Closed Lost</t>
         </is>
       </c>
       <c r="H1113" t="inlineStr">
@@ -78440,7 +78459,7 @@
         </is>
       </c>
       <c r="J1113" s="96" t="n">
-        <v>46255</v>
+        <v>46273</v>
       </c>
       <c r="K1113" s="96" t="n">
         <v>46255</v>
@@ -78554,7 +78573,7 @@
       </c>
       <c r="G1115" t="inlineStr">
         <is>
-          <t>Submitted</t>
+          <t>Intent to Award</t>
         </is>
       </c>
       <c r="H1115" t="inlineStr">
@@ -78586,12 +78605,4311 @@
           <t>Ashutosh Chauhan</t>
         </is>
       </c>
+      <c r="S1115" s="96" t="n">
+        <v>46265</v>
+      </c>
       <c r="Y1115" s="96" t="n">
         <v>46258</v>
       </c>
       <c r="Z1115" t="inlineStr">
         <is>
           <t>https://app.hubspot.com/contacts/243046792/record/0-3/343611945708</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>331925481149</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>2634-889</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>User Experience Design Consultant for WA Cares Fund</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Washington State Department of Social and Health Services</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1116" s="96" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K1116" s="96" t="n">
+        <v>46240</v>
+      </c>
+      <c r="L1116" t="n">
+        <v>56210</v>
+      </c>
+      <c r="M1116" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N1116" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1116" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1116" s="96" t="n">
+        <v>46196</v>
+      </c>
+      <c r="Z1116" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/331925481149</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>335261514487</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>SRC0000036055</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>ODJFS Child Support SETS Modernization RFP</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>Ohio Department of Job and Family Services</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1117" s="96" t="n">
+        <v>46255</v>
+      </c>
+      <c r="K1117" s="96" t="n">
+        <v>46255</v>
+      </c>
+      <c r="M1117" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="O1117" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1117" s="96" t="n">
+        <v>46217</v>
+      </c>
+      <c r="Z1117" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/335261514487</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>338920861370</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>SFUSD-PD-FY27#86</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Computerized Maintenance Management System (CMMS)</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>San Francisco Unified School District (SFUSD)</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1118" s="96" t="n">
+        <v>46254</v>
+      </c>
+      <c r="K1118" s="96" t="n">
+        <v>46254</v>
+      </c>
+      <c r="M1118" t="inlineStr">
+        <is>
+          <t>Platform Implementation (ERP, CRMs)</t>
+        </is>
+      </c>
+      <c r="O1118" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1118" s="96" t="n">
+        <v>46231</v>
+      </c>
+      <c r="Z1118" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/338920861370</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>339241439953</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>RFP No. #03-07.026</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>SaaS Consulting Services</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>Monroe County Community College</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1119" s="96" t="n">
+        <v>46240</v>
+      </c>
+      <c r="K1119" s="96" t="n">
+        <v>46240</v>
+      </c>
+      <c r="L1119" t="n">
+        <v>335275</v>
+      </c>
+      <c r="M1119" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N1119" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1119" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1119" s="96" t="n">
+        <v>46232</v>
+      </c>
+      <c r="Z1119" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/339241439953</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="n">
+        <v>1119</v>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>340222101204</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>270024</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Independent Voter Data Validation and Automation Protocol Design</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Jefferson County Clerk's Office (JCC)</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1120" s="96" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K1120" s="96" t="n">
+        <v>46248</v>
+      </c>
+      <c r="L1120" t="n">
+        <v>30400</v>
+      </c>
+      <c r="M1120" t="inlineStr">
+        <is>
+          <t>Audits and Assessment;Consulting</t>
+        </is>
+      </c>
+      <c r="N1120" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="O1120" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1120" s="96" t="n">
+        <v>46239</v>
+      </c>
+      <c r="Z1120" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340222101204</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="n">
+        <v>1120</v>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>340226297531</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Generative AI Training, Policy Development and Policy Implementation</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>MERRIMACK COUNTY</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1121" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K1121" s="96" t="n">
+        <v>46255</v>
+      </c>
+      <c r="M1121" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="O1121" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1121" s="96" t="n">
+        <v>46240</v>
+      </c>
+      <c r="Z1121" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340226297531</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="n">
+        <v>1121</v>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>340260896449</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>MANAGED INFORMATION TECHNOLOGY SERVICES</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>CITY OF BAYONNE</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1122" s="96" t="n">
+        <v>46248</v>
+      </c>
+      <c r="K1122" s="96" t="n">
+        <v>46248</v>
+      </c>
+      <c r="M1122" t="inlineStr">
+        <is>
+          <t>Consulting;Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N1122" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="O1122" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1122" s="96" t="n">
+        <v>46239</v>
+      </c>
+      <c r="Z1122" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340260896449</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="n">
+        <v>1122</v>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>340263700165</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>RFQ-ITS 26-0063</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Enterprise Resource Planning (ERP) Implementation Advisory Services</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>City of Davis</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1123" s="96" t="n">
+        <v>46253</v>
+      </c>
+      <c r="K1123" s="96" t="n">
+        <v>46253</v>
+      </c>
+      <c r="L1123" t="n">
+        <v>89720</v>
+      </c>
+      <c r="M1123" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N1123" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1123" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1123" s="96" t="n">
+        <v>46239</v>
+      </c>
+      <c r="Z1123" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340263700165</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="n">
+        <v>1123</v>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>340266535672</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>[Offline] Managed IT and Technical Support Services</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>TOWN OF MOUNT VERNON</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1124" s="96" t="n">
+        <v>46251</v>
+      </c>
+      <c r="K1124" s="96" t="n">
+        <v>46251</v>
+      </c>
+      <c r="L1124" t="n">
+        <v>138800</v>
+      </c>
+      <c r="M1124" t="inlineStr">
+        <is>
+          <t>Consulting;Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N1124" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="O1124" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1124" s="96" t="n">
+        <v>46240</v>
+      </c>
+      <c r="Z1124" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340266535672</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="n">
+        <v>1124</v>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>340491546352</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>CAPK SOW 2</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>Community Action Partnership of Kern</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1125" s="96" t="n">
+        <v>46244</v>
+      </c>
+      <c r="K1125" s="96" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O1125" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1125" s="96" t="n">
+        <v>46241</v>
+      </c>
+      <c r="Z1125" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340491546352</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="n">
+        <v>1125</v>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>340263702254</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Advanced Email Security</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>State of West Virginia</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1126" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K1126" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="O1126" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1126" s="96" t="n">
+        <v>46239</v>
+      </c>
+      <c r="Z1126" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340263702254</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="n">
+        <v>1126</v>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>343126350577</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Consulting and full stack development services for PORTAL and BikePed Portal</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>Portland State University</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1127" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="K1127" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="O1127" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1127" s="96" t="n">
+        <v>46255</v>
+      </c>
+      <c r="Z1127" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/343126350577</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="n">
+        <v>1127</v>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>337719148279</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Database Design and Application Development</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>Skagit Valley College</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1128" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="K1128" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="O1128" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1128" s="96" t="n">
+        <v>46226</v>
+      </c>
+      <c r="Z1128" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/337719148279</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="n">
+        <v>1128</v>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>339688035053</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>20673</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Managed Security Operations Center</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>County of Placer</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1129" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="K1129" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="O1129" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1129" s="96" t="n">
+        <v>46234</v>
+      </c>
+      <c r="Z1129" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/339688035053</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="n">
+        <v>1129</v>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>339204272847</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>EPA Year 1 IT Strategic Plan Implementation Support Services</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>City of East Palo Alto</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1130" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="K1130" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="L1130" t="n">
+        <v>112104</v>
+      </c>
+      <c r="M1130" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N1130" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1130" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1130" s="96" t="n">
+        <v>46232</v>
+      </c>
+      <c r="Z1130" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/339204272847</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="n">
+        <v>1130</v>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>340262204126</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>CAD/RMS Consultant</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>The County of Ontario</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1131" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="K1131" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="O1131" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1131" s="96" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Z1131" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340262204126</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="n">
+        <v>1131</v>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>334067536603</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>66114-27-RFP-0707</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>OFF - Managed Information Technology (IT) Services</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>City of Canton</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1132" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K1132" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="L1132" t="n">
+        <v>92000</v>
+      </c>
+      <c r="N1132" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="O1132" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1132" s="96" t="n">
+        <v>46211</v>
+      </c>
+      <c r="Z1132" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/334067536603</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="n">
+        <v>1132</v>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>342341006014</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>IT Managed Services Provider (MSP) Contract</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>Town of Milton</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1133" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K1133" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="L1133" t="n">
+        <v>150624</v>
+      </c>
+      <c r="M1133" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N1133" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1133" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1133" s="96" t="n">
+        <v>46251</v>
+      </c>
+      <c r="Z1133" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/342341006014</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="n">
+        <v>1133</v>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>339205651149</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Information Technology Managed Services</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>City of Maywood</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1134" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K1134" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="M1134" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O1134" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1134" s="96" t="n">
+        <v>46231</v>
+      </c>
+      <c r="Z1134" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/339205651149</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="n">
+        <v>1134</v>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>335797821128</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>OFFLINE Cloud Migration of Server Infrastructure</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>City of Cabot</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1135" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K1135" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="M1135" t="inlineStr">
+        <is>
+          <t>Modernization / Migration</t>
+        </is>
+      </c>
+      <c r="O1135" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1135" s="96" t="n">
+        <v>46218</v>
+      </c>
+      <c r="Z1135" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/335797821128</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="n">
+        <v>1135</v>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>340266175210</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>RFP No. 12-26</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>OFF - Managed IT Services</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>City of Pleasant Hill</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1136" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K1136" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="M1136" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N1136" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="O1136" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1136" s="96" t="n">
+        <v>46244</v>
+      </c>
+      <c r="Z1136" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340266175210</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="n">
+        <v>1136</v>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>337949148879</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Managed Technology Services</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>City of Isle of Palms</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1137" s="96" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K1137" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="O1137" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1137" s="96" t="n">
+        <v>46226</v>
+      </c>
+      <c r="Z1137" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/337949148879</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="n">
+        <v>1137</v>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>341673935590</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>6895</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Third-Party Microsoft Support Svcs</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>Washtenaw Community College</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1138" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="K1138" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="M1138" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="O1138" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1138" s="96" t="n">
+        <v>46246</v>
+      </c>
+      <c r="Z1138" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/341673935590</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="n">
+        <v>1138</v>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>337719147232</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>GIS Support Services</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>CITY OF NEW BRITAIN</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1139" s="96" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K1139" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="O1139" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1139" s="96" t="n">
+        <v>46226</v>
+      </c>
+      <c r="Z1139" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/337719147232</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="n">
+        <v>1139</v>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>340877955802</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Public Safety Software Consulting</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>Rockingham County Emergency Communications</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1140" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1140" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="O1140" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1140" s="96" t="n">
+        <v>46245</v>
+      </c>
+      <c r="Z1140" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340877955802</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="n">
+        <v>1140</v>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>339872705212</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>MANAGED SECURITY SERVICES PROVIDER</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>Columbus Regional Airport Authority</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1141" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K1141" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="O1141" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1141" s="96" t="n">
+        <v>46235</v>
+      </c>
+      <c r="Z1141" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/339872705212</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="n">
+        <v>1141</v>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>340227097294</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>RFQ-ITS 26-0063</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>Project Portfolio Management (PPM) Dashboard</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>Department of Forestry and Fire Protection (CAL FIRE)</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1142" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K1142" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="M1142" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N1142" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1142" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1142" s="96" t="n">
+        <v>46241</v>
+      </c>
+      <c r="Z1142" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340227097294</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="n">
+        <v>1142</v>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>342330119868</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Staff Augmentation for IBM iSeries</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>University of Minnesota</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1143" s="96" t="n">
+        <v>46261</v>
+      </c>
+      <c r="K1143" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="O1143" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1143" s="96" t="n">
+        <v>46251</v>
+      </c>
+      <c r="Z1143" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/342330119868</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="n">
+        <v>1143</v>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>339559107311</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>EPA vCISO Support Services</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>City of East Palo Alto</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1144" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K1144" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="M1144" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N1144" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1144" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1144" s="96" t="n">
+        <v>46234</v>
+      </c>
+      <c r="Z1144" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/339559107311</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="n">
+        <v>1144</v>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>335262883519</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>OFF - MAPPING AND GEOGRAPHIC INFORMATION SERVICES (GIS)</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>City of Canton</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1145" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="K1145" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="O1145" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1145" s="96" t="n">
+        <v>46216</v>
+      </c>
+      <c r="Z1145" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/335262883519</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="n">
+        <v>1145</v>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>340222697182</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>26-084</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Enterprise Digital Accessibility Consulting and ADA Compliance Services</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>City of College Station</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1146" s="96" t="n">
+        <v>46261</v>
+      </c>
+      <c r="K1146" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="O1146" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1146" s="96" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Z1146" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340222697182</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="n">
+        <v>1146</v>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>339242259167</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>HubSpot Design, Implementation, and Support Services IDIQ</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>Port of Seattle</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1147" s="96" t="n">
+        <v>46261</v>
+      </c>
+      <c r="K1147" s="96" t="n">
+        <v>46261</v>
+      </c>
+      <c r="O1147" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1147" s="96" t="n">
+        <v>46233</v>
+      </c>
+      <c r="Z1147" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/339242259167</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="n">
+        <v>1147</v>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>340263576281</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Digital Accessibility Services</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>Contra Costa Water District</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1148" s="96" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K1148" s="96" t="n">
+        <v>46261</v>
+      </c>
+      <c r="O1148" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1148" s="96" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Z1148" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340263576281</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="n">
+        <v>1148</v>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>340221250244</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>27-022-TUSD1</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Enterprise Resource Planning (ERP) Strategy, Procurement, and Implementation Consulting Services</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>Tucson Unified School District</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1149" s="96" t="n">
+        <v>46261</v>
+      </c>
+      <c r="K1149" s="96" t="n">
+        <v>46261</v>
+      </c>
+      <c r="M1149" t="inlineStr">
+        <is>
+          <t>Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N1149" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="O1149" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1149" s="96" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Z1149" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340221250244</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="n">
+        <v>1149</v>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>337549681365</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>2026-RFP-DP-003</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>Consulting Services to Advise on Artificial Intelligence (AI) Use</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>Housing Authority of the City of Alameda</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1150" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="K1150" s="96" t="n">
+        <v>46261</v>
+      </c>
+      <c r="M1150" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="O1150" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1150" s="96" t="n">
+        <v>46226</v>
+      </c>
+      <c r="Z1150" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/337549681365</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>343825812216</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Investment Data Warehouse (IDW) Technical Resources</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>California State Teachers' Retirement System</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1151" s="96" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K1151" s="96" t="n">
+        <v>46262</v>
+      </c>
+      <c r="O1151" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1151" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="Z1151" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/343825812216</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="n">
+        <v>1151</v>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>340785154807</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>2026-001-049</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>Managed Email Security Solution RFP</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>Cherokee Nation Business</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1152" s="96" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K1152" s="96" t="n">
+        <v>46262</v>
+      </c>
+      <c r="M1152" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O1152" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1152" s="96" t="n">
+        <v>46244</v>
+      </c>
+      <c r="Z1152" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340785154807</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="n">
+        <v>1152</v>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>340227330770</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>FHA-RFP2026-01</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>OFFLINE Managed IT Services</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>Franklin Housing Authority</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1153" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1153" s="96" t="n">
+        <v>46262</v>
+      </c>
+      <c r="M1153" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O1153" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1153" s="96" t="n">
+        <v>46244</v>
+      </c>
+      <c r="Z1153" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340227330770</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="n">
+        <v>1153</v>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>337284643518</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Managed Information Technology Consulting Services</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>Village of Inverness</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1154" s="96" t="n">
+        <v>46261</v>
+      </c>
+      <c r="K1154" s="96" t="n">
+        <v>46262</v>
+      </c>
+      <c r="O1154" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1154" s="96" t="n">
+        <v>46224</v>
+      </c>
+      <c r="Z1154" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/337284643518</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="n">
+        <v>1154</v>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>340785149663</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>RFP 2026-005</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>IT Managed Services RFP (Re-Issue)</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>Regional Transit Authority of Southeast Michigan</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1155" s="96" t="n">
+        <v>46262</v>
+      </c>
+      <c r="K1155" s="96" t="n">
+        <v>46262</v>
+      </c>
+      <c r="L1155" t="n">
+        <v>222207.22</v>
+      </c>
+      <c r="M1155" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="N1155" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="O1155" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1155" s="96" t="n">
+        <v>46244</v>
+      </c>
+      <c r="Z1155" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340785149663</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="n">
+        <v>1155</v>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>343126348490</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>IT Managed Services Provider</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>Community Desk Chicago</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1156" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1156" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="O1156" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1156" s="96" t="n">
+        <v>46255</v>
+      </c>
+      <c r="Z1156" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/343126348490</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="n">
+        <v>1156</v>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>343958642382</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>IT-RFP-2026</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Request for Proposal (RFP) for Technology Services</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>The Center for Law and Social Policy (CLASP)</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>District of Columbia</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1157" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1157" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L1157" t="n">
+        <v>54360</v>
+      </c>
+      <c r="M1157" t="inlineStr">
+        <is>
+          <t>Consulting;Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O1157" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1157" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="Z1157" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/343958642382</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="n">
+        <v>1157</v>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>340227089087</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>Salesforce &amp; Systems Administrator</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>Canopy</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1158" s="96" t="n">
+        <v>46266</v>
+      </c>
+      <c r="K1158" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="O1158" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1158" s="96" t="n">
+        <v>46241</v>
+      </c>
+      <c r="Z1158" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340227089087</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="n">
+        <v>1158</v>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>333486453483</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>2025-19</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Microsoft 365 and Related Cloud Services Development, Administration, and Support</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>Covered California</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1159" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1159" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="O1159" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1159" s="96" t="n">
+        <v>46203</v>
+      </c>
+      <c r="Z1159" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/333486453483</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="n">
+        <v>1159</v>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>343124343538</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>PROFESSIONAL SERVICES</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Rice Creek Watershed District</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1160" s="96" t="n">
+        <v>46269</v>
+      </c>
+      <c r="K1160" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M1160" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP);Consulting</t>
+        </is>
+      </c>
+      <c r="N1160" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1160" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1160" s="96" t="n">
+        <v>46257</v>
+      </c>
+      <c r="Z1160" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/343124343538</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="n">
+        <v>1160</v>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>340614390470</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>123978</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Technical Services for Networking and Infrastructure</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>Alexandria City public schools</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1161" s="96" t="n">
+        <v>46266</v>
+      </c>
+      <c r="K1161" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M1161" t="inlineStr">
+        <is>
+          <t>Consulting;Managed Services (MSP);Audits and Assessment</t>
+        </is>
+      </c>
+      <c r="N1161" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+      <c r="O1161" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1161" s="96" t="n">
+        <v>46241</v>
+      </c>
+      <c r="Z1161" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340614390470</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="n">
+        <v>1161</v>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>341765379791</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Managed End-Point Detection and Response Software and Services</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>City of Biloxi</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1162" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1162" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M1162" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O1162" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Q1162" s="96" t="n">
+        <v>46275</v>
+      </c>
+      <c r="Y1162" s="96" t="n">
+        <v>46247</v>
+      </c>
+      <c r="Z1162" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/341765379791</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="n">
+        <v>1162</v>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>339566252749</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>Managed Information Technology Services, Microsoft 365 Migration, and Microsoft Licensing</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>Town of Madison</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1163" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1163" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M1163" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O1163" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1163" s="96" t="n">
+        <v>46234</v>
+      </c>
+      <c r="Z1163" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/339566252749</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="n">
+        <v>1163</v>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>342018932418</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>Dashboard and Scorecard System for Public Health Program Performance</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>BUNCOMBE COUNTY</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1164" s="96" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K1164" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="N1164" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1164" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1164" s="96" t="n">
+        <v>46241</v>
+      </c>
+      <c r="Z1164" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/342018932418</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="n">
+        <v>1164</v>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>343587778289</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>Salesforce System Enhancement &amp; Optimization</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>Umoja Community Education Fund (UCEF)</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1165" s="96" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K1165" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="N1165" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1165" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1165" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="Z1165" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/343587778289</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="n">
+        <v>1165</v>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>340265815743</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>Customer Support System</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>Massachusetts Office of the Inspector General</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1166" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1166" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="O1166" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1166" s="96" t="n">
+        <v>46240</v>
+      </c>
+      <c r="Z1166" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340265815743</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="n">
+        <v>1166</v>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>340222691003</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>Retainer Contract Opportunity for Information Technology (IT) Services</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>State of Vermont (Department of Buildings and General Services)</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Vermont</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1167" s="96" t="n">
+        <v>46267</v>
+      </c>
+      <c r="K1167" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M1167" t="inlineStr">
+        <is>
+          <t>Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="O1167" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1167" s="96" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Z1167" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340222691003</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>340223358656</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>Information Technology Services</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>Orange County Employees Retirement System (OCERS)</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1168" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1168" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="O1168" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1168" s="96" t="n">
+        <v>46238</v>
+      </c>
+      <c r="Z1168" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340223358656</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="n">
+        <v>1168</v>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>344147314377</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>BD-26-340-3401-1993</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>FortiGate and FortiSwitch License Renewal and Support Services</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>Virgin Islands Bureau of Internal Revenue (VIBI)</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Virgin Islands</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1169" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1169" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L1169" t="n">
+        <v>48530.26</v>
+      </c>
+      <c r="M1169" t="inlineStr">
+        <is>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="N1169" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1169" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1169" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="Z1169" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/344147314377</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="n">
+        <v>1169</v>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>342172723922</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>On-site Information Technology Consultant Services</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Stony Brook University Hospital</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>Closed Lost</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1170" s="96" t="n">
+        <v>46273</v>
+      </c>
+      <c r="K1170" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="O1170" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1170" s="96" t="n">
+        <v>46248</v>
+      </c>
+      <c r="Z1170" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/342172723922</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="n">
+        <v>1170</v>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>342942703295</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>GEOGRAPHICAL INFORMATION SYSTEMS (GIS) PROFESSIONAL SUPPORT SERVICES</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>Laguna Beach</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1171" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1171" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="O1171" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1171" s="96" t="n">
+        <v>46252</v>
+      </c>
+      <c r="Z1171" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/342942703295</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>337549680364</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>26RFP-26-09RHT-021</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Rural Health Data Atlas- Data Visualization and Analysis Platform</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>South Dakota Department of Health</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1172" s="96" t="n">
+        <v>46266</v>
+      </c>
+      <c r="K1172" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L1172" t="n">
+        <v>374000</v>
+      </c>
+      <c r="M1172" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="N1172" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="O1172" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1172" s="96" t="n">
+        <v>46226</v>
+      </c>
+      <c r="Z1172" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/337549680364</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>344949853888</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District - SOW 5</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1173" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1173" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="L1173" t="n">
+        <v>266240</v>
+      </c>
+      <c r="M1173" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP);Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="O1173" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S1173" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="Y1173" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="Z1173" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/344949853888</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>344730713824</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District - Workday Business Analyst Services - SOW 6</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K1174" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L1174" t="n">
+        <v>173584.52</v>
+      </c>
+      <c r="M1174" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP);Staff Augmentation</t>
+        </is>
+      </c>
+      <c r="O1174" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S1174" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="Y1174" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="Z1174" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/344730713824</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>343124160225</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Website Strategy, Redesign, Development, and Managed Digital Services</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>BBOP Center</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>District of Columbia</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1175" s="96" t="n">
+        <v>46272</v>
+      </c>
+      <c r="K1175" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M1175" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="O1175" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1175" s="96" t="n">
+        <v>46255</v>
+      </c>
+      <c r="Z1175" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/343124160225</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>337433980658</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>IMP - Information Technology (IT) Managed Services</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>Mesa Water District</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1176" s="96" t="n">
+        <v>46268</v>
+      </c>
+      <c r="K1176" s="96" t="n">
+        <v>46268</v>
+      </c>
+      <c r="M1176" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O1176" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1176" s="96" t="n">
+        <v>46225</v>
+      </c>
+      <c r="Z1176" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/337433980658</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="n">
+        <v>1176</v>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>343946947277</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>AWS Server Administration</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Conservation Commission</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1177" s="96" t="n">
+        <v>46269</v>
+      </c>
+      <c r="K1177" s="96" t="n">
+        <v>46269</v>
+      </c>
+      <c r="O1177" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1177" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="Z1177" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/343946947277</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="n">
+        <v>1177</v>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>339208506046</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>No. VW0667</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>Web Development and Hosting Services</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>Santa Clara Valley Water District</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1178" s="96" t="n">
+        <v>46269</v>
+      </c>
+      <c r="K1178" s="96" t="n">
+        <v>46269</v>
+      </c>
+      <c r="O1178" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1178" s="96" t="n">
+        <v>46233</v>
+      </c>
+      <c r="Z1178" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/339208506046</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="n">
+        <v>1178</v>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>340785869529</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Case Management System (CMS) Modernization Technical Assistance</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>San Diego County</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>Intent to Award</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1179" s="96" t="n">
+        <v>46252</v>
+      </c>
+      <c r="L1179" t="n">
+        <v>275000</v>
+      </c>
+      <c r="O1179" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="S1179" s="96" t="n">
+        <v>46261</v>
+      </c>
+      <c r="Y1179" s="96" t="n">
+        <v>46244</v>
+      </c>
+      <c r="Z1179" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/340785869529</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="n">
+        <v>1179</v>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>341673938630</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>Business Crucial IT Consulting and Managed Services</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>Town of Erie</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1180" s="96" t="n">
+        <v>46276</v>
+      </c>
+      <c r="O1180" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1180" s="96" t="n">
+        <v>46246</v>
+      </c>
+      <c r="Z1180" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/341673938630</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="n">
+        <v>1180</v>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>343185485500</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>Figma for Government FY27 Renewal</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>Department of Public Safety (Ohio)</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1181" s="96" t="n">
+        <v>46267</v>
+      </c>
+      <c r="O1181" t="inlineStr">
+        <is>
+          <t>Hrithik Srivastava</t>
+        </is>
+      </c>
+      <c r="Y1181" s="96" t="n">
+        <v>46255</v>
+      </c>
+      <c r="Z1181" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/343185485500</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="n">
+        <v>1181</v>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>343825824480</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>AI Assessment Services</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>Illinois Housing Development Authority</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1182" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="O1182" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1182" s="96" t="n">
+        <v>46259</v>
+      </c>
+      <c r="Z1182" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/343825824480</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="n">
+        <v>1182</v>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>344318357212</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>Cisco Meraki Licenses and Support</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Clay County</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1183" s="96" t="n">
+        <v>46273</v>
+      </c>
+      <c r="K1183" s="96" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M1183" t="inlineStr">
+        <is>
+          <t>Reseller</t>
+        </is>
+      </c>
+      <c r="O1183" t="inlineStr">
+        <is>
+          <t>Ashutosh Chauhan</t>
+        </is>
+      </c>
+      <c r="Y1183" s="96" t="n">
+        <v>46260</v>
+      </c>
+      <c r="Z1183" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/344318357212</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="n">
+        <v>1183</v>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>335175760588</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>2026-020</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>360° MANAGED IT SERVICES</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>New Orleans Regional Transit Authority</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>RFx Cancelled</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1184" s="96" t="n">
+        <v>46255</v>
+      </c>
+      <c r="K1184" s="96" t="n">
+        <v>46254</v>
+      </c>
+      <c r="M1184" t="inlineStr">
+        <is>
+          <t>Managed Services (MSP)</t>
+        </is>
+      </c>
+      <c r="O1184" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1184" s="96" t="n">
+        <v>46213</v>
+      </c>
+      <c r="Z1184" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/335175760588</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="n">
+        <v>1184</v>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>345155887843</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>EOG-RFQ-27-03</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>Enterprise Cybersecurity Compliance Audits Testing and Support &amp; NIST CSF Ground-Truth and Ad-Hoc Testing</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>Florida Offices of Inspector General (OIG)</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1185" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1185" s="96" t="n">
+        <v>46264</v>
+      </c>
+      <c r="M1185" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="O1185" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1185" s="96" t="n">
+        <v>46266</v>
+      </c>
+      <c r="Z1185" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/345155887843</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="n">
+        <v>1185</v>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>345157328607</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>EOG-RFQ-27-04</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>Cybersecurity Subject Matter Expertise and Audit Enablement Services</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>Florida Offices of Inspector General (OIG)</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J1186" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K1186" s="96" t="n">
+        <v>46264</v>
+      </c>
+      <c r="O1186" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="Y1186" s="96" t="n">
+        <v>46266</v>
+      </c>
+      <c r="Z1186" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/345157328607</t>
         </is>
       </c>
     </row>
@@ -78612,7 +82930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA98"/>
+  <dimension ref="A1:AA102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -87116,6 +91434,223 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>344949853888</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District - SOW 5</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="J99" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K99" s="96" t="n">
+        <v>46258</v>
+      </c>
+      <c r="L99" t="n">
+        <v>266240</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S99" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="Y99" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/344949853888</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>344730713824</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District - Workday Business Analyst Services - SOW 6</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Madison Metropolitan Sewerage District</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="K100" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="L100" t="n">
+        <v>173584.52</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Madhav Mitruka</t>
+        </is>
+      </c>
+      <c r="S100" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="Y100" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/344730713824</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>337552991947</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ServiceNow Virtual Agent Implementation</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Minnesota Judicial Branch</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="J101" s="96" t="n">
+        <v>46265</v>
+      </c>
+      <c r="K101" s="96" t="n">
+        <v>46237</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="U101" s="96" t="n">
+        <v>46254</v>
+      </c>
+      <c r="Y101" s="96" t="n">
+        <v>46226</v>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/337552991947</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>332610669272</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>City of Cleveland - Software Maintenance</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>City of Cleveland</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="J102" s="96" t="n">
+        <v>46268</v>
+      </c>
+      <c r="K102" s="96" t="n">
+        <v>46202</v>
+      </c>
+      <c r="L102" t="n">
+        <v>17600</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Yash More</t>
+        </is>
+      </c>
+      <c r="S102" s="96" t="n">
+        <v>46226</v>
+      </c>
+      <c r="U102" s="96" t="n">
+        <v>46226</v>
+      </c>
+      <c r="Y102" s="96" t="n">
+        <v>46199</v>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>https://app.hubspot.com/contacts/243046792/record/0-3/332610669272</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AA85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
